--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -413,205 +413,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>lob_name</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>source_weight</t>
+          <t>severity</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>target_weight</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>line_level_ratio</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>projected_contribution</t>
+          <t>multiplier</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>raw donor</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.011495</v>
+        <v>0.052376</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.052376</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.013094</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Casualty</t>
+          <t>after size</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.050688</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
+        <v>0.967778</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marine</t>
+          <t>after concentration (adjusted)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.044848</v>
       </c>
       <c r="C4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Aviation</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.481108</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.052376</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Reinsurance — Property</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Professional Lines</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Accident &amp; Health</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Cyber</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Aggregate</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.507397</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.052376</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
+        <v>0.8847699999999999</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.052376</v>
+        <v>5e-06</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.050688</v>
+        <v>5e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>0.967778</v>
+        <v>0.900459</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.044848</v>
+        <v>4e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8847699999999999</v>
+        <v>0.858114</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -456,7 +456,7 @@
         <v>5e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>0.900459</v>
+        <v>0.898644</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>4e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>0.858114</v>
+        <v>0.865738</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -456,7 +456,7 @@
         <v>5e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>0.898644</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>4e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>0.865738</v>
+        <v>0.868233</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -456,7 +456,7 @@
         <v>5e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>0.901</v>
+        <v>0.900763</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>4e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>0.868233</v>
+        <v>0.8700830000000001</v>
       </c>
     </row>
   </sheetData>
